--- a/descubrir/02-descarte-y-filtros/plantilla-descarte.xlsx
+++ b/descubrir/02-descarte-y-filtros/plantilla-descarte.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Descartadas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sobrevivientes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finalistas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Descartadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sobrevivientes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Finalistas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -96,6 +96,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -735,15 +738,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -759,15 +764,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>¿Qué problema, y de quién?</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>¿Con quién hablamos?</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>¿Quién lo consigue?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>¿Qué necesita que hoy no tengamos?</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Revisión</t>
         </is>
@@ -781,11 +796,15 @@
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Las que pasaron los tres cortes.
-• «¿Con quién hablamos?» se responde con un nombre o un lugar concreto. Un tipo de persona no cuenta.
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Las que pasaron los tres cortes. Una columna por corte: sin lo que ustedes escribieron ahí, la revisión no tiene qué leer.
+• «¿Qué problema, y de quién?» — corte 1. Si no se puede escribir como problema de alguien, no había problema detrás.
+• «¿Con quién hablamos?» — corte 2. Un nombre o un lugar concreto. Un tipo de persona no cuenta.
 • «¿Quién lo consigue?» es alguien del equipo, con nombre.
+• «¿Qué necesita que hoy no tengamos?» — corte 3. Licencia, permiso, laboratorio, obra. Si no falta nada, escriban «nada».
 • La columna Revisión la llena la herramienta.</t>
         </is>
       </c>
@@ -798,6 +817,8 @@
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -807,6 +828,8 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -816,6 +839,8 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -825,6 +850,8 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -834,6 +861,8 @@
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -843,6 +872,8 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="n">
@@ -852,6 +883,8 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -861,6 +894,8 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -870,6 +905,8 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -879,6 +916,8 @@
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="n">
@@ -888,6 +927,8 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -897,6 +938,8 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="n">
@@ -906,6 +949,8 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -915,6 +960,8 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -924,6 +971,8 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -933,6 +982,8 @@
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="n">
@@ -942,6 +993,8 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -951,6 +1004,8 @@
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="n">
@@ -960,6 +1015,8 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -969,6 +1026,8 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="n">
@@ -978,6 +1037,8 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="n">
@@ -987,6 +1048,8 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="n">
@@ -996,16 +1059,13 @@
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G2:G9"/>
+    <mergeCell ref="I2:I9"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"sí,no"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1055,9 +1115,9 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Deseabilidad — ¿alguien lo quiere de verdad?</t>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Nombre del finalista</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -1067,6 +1127,7 @@
       <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Los tres que quedaron, comparados.
+• Los nombres de los tres van en la fila «Nombre del finalista», en B2, C2 y D2. Sin ellos la revisión solo puede decir «el ②».
 • Estos cuatro criterios no son binarios: tienen matices y de eso se trata la conversación.
 • El cuarto es el que más se deja en blanco y el que más pesa en un plazo corto.
 • «Nos parece interesante» no es encaje: encaje es qué sabe este equipo, a quién conoce y a qué tiene acceso.</t>
@@ -1076,7 +1137,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Factibilidad — ¿se puede construir con lo que existe hoy?</t>
+          <t>Deseabilidad — ¿alguien lo quiere de verdad?</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>
@@ -1087,7 +1148,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Viabilidad — ¿hay forma de que se sostenga?</t>
+          <t>Factibilidad — ¿se puede construir con lo que existe hoy?</t>
         </is>
       </c>
       <c r="B4" s="3" t="n"/>
@@ -1098,7 +1159,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Encaje con el equipo — ¿lo podemos hacer NOSOTROS?</t>
+          <t>Viabilidad — ¿hay forma de que se sostenga?</t>
         </is>
       </c>
       <c r="B5" s="3" t="n"/>
@@ -1106,7 +1167,17 @@
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
     </row>
-    <row r="6"/>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Encaje con el equipo — ¿lo podemos hacer NOSOTROS?</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+    </row>
     <row r="7"/>
     <row r="8"/>
     <row r="9"/>

--- a/descubrir/02-descarte-y-filtros/plantilla-descarte.xlsx
+++ b/descubrir/02-descarte-y-filtros/plantilla-descarte.xlsx
@@ -461,15 +461,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -485,10 +486,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Origen</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>El motivo que dimos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Revisión</t>
         </is>
@@ -501,12 +507,15 @@
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="E2" s="3" t="n"/>
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Una fila por idea que botaron.
 • El motivo va con las palabras de ustedes, no en bonito. «Ya existe algo así» se escribe tal cual.
 • Sin motivo escrito la revisión no sirve: el filtro es el razonamiento, no la lista.
-• La columna Revisión la llena la herramienta. Déjenla vacía.</t>
+• Origen viene de la herramienta anterior: P si la idea salió de un problema que ustedes observaron, S si salió de SCAMPER, X si la sugirió una IA.
+• La columna Revisión la llena la herramienta. Déjenla vacía.
+• El marcador de abajo cuenta tres cosas: las casillas de Revisión con texto, las celdas que escribieron ustedes, y las ideas que quedaron sin motivo. Anoten los dos últimos números antes de mandar el archivo: tienen que volver iguales.</t>
         </is>
       </c>
     </row>
@@ -517,6 +526,7 @@
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -525,6 +535,7 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -533,6 +544,7 @@
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -541,6 +553,7 @@
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -549,6 +562,7 @@
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -557,6 +571,7 @@
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="n">
@@ -565,6 +580,7 @@
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -573,6 +589,7 @@
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -581,13 +598,14 @@
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Descartes revisados</t>
-        </is>
-      </c>
-      <c r="G11">
-        <f>COUNTA(D2:D25)</f>
+      <c r="E11" s="3" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Casillas con tinta</t>
+        </is>
+      </c>
+      <c r="H11">
+        <f>COUNTA(E2:E25)</f>
         <v/>
       </c>
     </row>
@@ -598,13 +616,14 @@
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Motivos escritos</t>
-        </is>
-      </c>
-      <c r="G12">
-        <f>COUNTA(C2:C25)</f>
+      <c r="E12" s="3" t="n"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Puño del equipo</t>
+        </is>
+      </c>
+      <c r="H12">
+        <f>COUNTA(B2:D25)</f>
         <v/>
       </c>
     </row>
@@ -615,13 +634,14 @@
       <c r="B13" s="3" t="n"/>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Sin motivo</t>
-        </is>
-      </c>
-      <c r="G13">
-        <f>COUNTA(B2:B25)-COUNTA(C2:C25)</f>
+      <c r="E13" s="3" t="n"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Ideas huérfanas</t>
+        </is>
+      </c>
+      <c r="H13">
+        <f>COUNTA(B2:B25)-COUNTA(D2:D25)</f>
         <v/>
       </c>
     </row>
@@ -632,6 +652,7 @@
       <c r="B14" s="3" t="n"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="n">
@@ -640,6 +661,7 @@
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -648,6 +670,7 @@
       <c r="B16" s="3" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -656,6 +679,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -664,6 +688,7 @@
       <c r="B18" s="3" t="n"/>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="n">
@@ -672,6 +697,7 @@
       <c r="B19" s="3" t="n"/>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -680,6 +706,7 @@
       <c r="B20" s="3" t="n"/>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="n">
@@ -688,6 +715,7 @@
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -696,6 +724,7 @@
       <c r="B22" s="3" t="n"/>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="n">
@@ -704,6 +733,7 @@
       <c r="B23" s="3" t="n"/>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="n">
@@ -712,6 +742,7 @@
       <c r="B24" s="3" t="n"/>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="n">
@@ -720,11 +751,17 @@
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="F2:F9"/>
+    <mergeCell ref="G2:G9"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor poco usual" error="Se esperaba P, S o X. Puede continuar, pero revise que no sea un error de dedo." promptTitle="Origen de la idea" prompt="P = problema que ustedes observaron · S = SCAMPER · X = se la sugirió una IA" type="list" errorStyle="warning">
+      <formula1>"P,S,X"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -735,15 +772,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -759,15 +797,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Origen</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>¿Con quién hablamos?</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>¿Quién lo consigue?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Revisión</t>
         </is>
@@ -781,11 +824,13 @@
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="F2" s="3" t="n"/>
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Las que pasaron los tres cortes.
 • «¿Con quién hablamos?» se responde con un nombre o un lugar concreto. Un tipo de persona no cuenta.
-• «¿Quién lo consigue?» es alguien del equipo, con nombre.
+• «¿Quién lo consigue?» es alguien del equipo, con nombre. Los dos van juntos: contacto sin responsable no es un contacto.
+• Origen: P si la idea salió de un problema que ustedes observaron, S si salió de SCAMPER, X si la sugirió una IA.
 • La columna Revisión la llena la herramienta.</t>
         </is>
       </c>
@@ -798,6 +843,7 @@
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -807,6 +853,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -816,6 +863,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -825,6 +873,7 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -834,6 +883,7 @@
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -843,6 +893,7 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="n">
@@ -852,6 +903,7 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -861,6 +913,7 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -870,6 +923,7 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -879,6 +933,7 @@
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="n">
@@ -888,6 +943,7 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -897,6 +953,7 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="n">
@@ -906,6 +963,7 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -915,6 +973,7 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -924,6 +983,7 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -933,6 +993,7 @@
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="n">
@@ -942,6 +1003,7 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -951,6 +1013,7 @@
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="n">
@@ -960,6 +1023,7 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -969,6 +1033,7 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="n">
@@ -978,6 +1043,7 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="n">
@@ -987,6 +1053,7 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="n">
@@ -996,15 +1063,18 @@
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G2:G9"/>
+    <mergeCell ref="H2:H9"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"sí,no"</formula1>
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor poco usual" error="Se esperaba P, S o X. Puede continuar, pero revise que no sea un error de dedo." promptTitle="Origen de la idea" prompt="P = problema que ustedes observaron · S = SCAMPER · X = se la sugirió una IA" type="list" errorStyle="warning">
+      <formula1>"P,S,X"</formula1>
     </dataValidation>
+    <dataValidation sqref="D2:D25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="¿Con quién hablamos?" prompt="Un nombre o un lugar concreto, escrito a mano. Un tipo de persona no cuenta."/>
+    <dataValidation sqref="E2:E25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="¿Quién lo consigue?" prompt="Alguien del equipo, con nombre. Es la mitad que casi nadie escribe."/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1067,9 +1137,11 @@
       <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Los tres que quedaron, comparados.
+• Escriban el nombre de cada finalista en la fila 1, al lado de su número.
 • Estos cuatro criterios no son binarios: tienen matices y de eso se trata la conversación.
 • El cuarto es el que más se deja en blanco y el que más pesa en un plazo corto.
-• «Nos parece interesante» no es encaje: encaje es qué sabe este equipo, a quién conoce y a qué tiene acceso.</t>
+• «Nos parece interesante» no es encaje: encaje es qué sabe este equipo, a quién conoce y a qué tiene acceso.
+• El origen de cada finalista ya está en la hoja Sobrevivientes: acá no se repite.</t>
         </is>
       </c>
     </row>
